--- a/app/export_resumo_resultados.xlsx
+++ b/app/export_resumo_resultados.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pierre Goncalves</t>
+          <t>Acucena Pinto Romero</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,52 +457,502 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60.23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gustavo Giotto</t>
+          <t>Anahis Del Jesus Marquez Zapata</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Refilador Perna 2T</t>
+          <t>Refilador Peito 1T</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61.29</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nelvande Bizerra</t>
+          <t>Andrisa Ribeiro dos Santos</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Refilador Perna 1T</t>
+          <t>Refilador Peito 1T</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60.43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rudson Frigotto</t>
+          <t>Anerkis Francisca Reina</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Refilador Peito 2T</t>
+          <t>Refilador Peito 1T</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.59999999999999</v>
+        <v>43.33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Darin Giovanna Lopez Bellorin</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>45.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Deborah Martinez Montes de Oca</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Delis Teresa Guilarte Guilarte</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>55.43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Doreen Elena Viamonte Rodriguez</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Estefany Eliana Vasquez Eurea</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>42.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Evelin Del Carmen Aguilera de Romero</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Francieli Medeiros da Silva</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Glorianny Delvalle Lugo Flores</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gorete dos Santos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Iliana Maribel Bonalde Pantoja</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jocelaine Moura de Souza</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Juvilda Chaves Sardi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>35.33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Laydee Rosa Mejias Medina</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>63.45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lismar Del Valle Moreno Leonett</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>36.57</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Loysineth Hamara De Los Angeles Salazar Gomez</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Maria Alejandra Lopez Mejias</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Maria Helena Pontin</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Maria Milagros Tabares Pantoja</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Maria Soledad Guilarte Hernandez</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Marice Castell Pena</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Milexi Alejandra Zue Farias</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>30.67</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sara Yslei Conceicao Nascimento</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>51.43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sinara Daiane Rodrigues</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Viannexis Iralis Aray Farias</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Yohana Carolina Zorrilla</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>74.29000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Yuliangel José Brito Gonzalez</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Zulecxy Hecdunelyn Ortiz Hernandez</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Andresa Almeida Castilhos</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Refilador Sobrecoxa 1T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Rafaelina Del Valle Cardozo Martinez</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>43.33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Rita Bianca da Silva Valau</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Refilador Peito 1T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
